--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129618407</v>
       </c>
       <c r="B2" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,45 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>97627</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R4" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -958,61 +962,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>97639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R5" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,49 +1059,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1110,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R6" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1146,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,38 +1178,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R7" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1248,11 +1253,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,49 +1671,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618548</v>
+        <v>129617528</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621673</v>
+        <v>621607</v>
       </c>
       <c r="R12" t="n">
-        <v>7055206</v>
+        <v>7055257</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1746,6 +1747,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617528</v>
+        <v>129618470</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,39 +1789,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621607</v>
+        <v>621654</v>
       </c>
       <c r="R13" t="n">
-        <v>7055257</v>
+        <v>7055226</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1848,11 +1844,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,40 +1870,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B14" t="n">
-        <v>92000</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R14" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1974,7 +1974,7 @@
         <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129617589</v>
       </c>
       <c r="B17" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129618407</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129620602</v>
+        <v>129618470</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>92007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621557</v>
+        <v>621654</v>
       </c>
       <c r="R11" t="n">
-        <v>7055312</v>
+        <v>7055226</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,50 +1666,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617528</v>
+        <v>129618548</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621607</v>
+        <v>621673</v>
       </c>
       <c r="R12" t="n">
-        <v>7055257</v>
+        <v>7055206</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,11 +1741,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618470</v>
+        <v>129620602</v>
       </c>
       <c r="B13" t="n">
-        <v>92006</v>
+        <v>91588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,29 +1778,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621654</v>
+        <v>621557</v>
       </c>
       <c r="R13" t="n">
-        <v>7055226</v>
+        <v>7055312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1870,49 +1864,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618548</v>
+        <v>129617528</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621673</v>
+        <v>621607</v>
       </c>
       <c r="R14" t="n">
-        <v>7055206</v>
+        <v>7055257</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,7 +1974,7 @@
         <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129617589</v>
       </c>
       <c r="B17" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129618470</v>
+        <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>92007</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,29 +1585,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621654</v>
+        <v>621557</v>
       </c>
       <c r="R11" t="n">
-        <v>7055226</v>
+        <v>7055312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1666,49 +1671,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618548</v>
+        <v>129617528</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621673</v>
+        <v>621607</v>
       </c>
       <c r="R12" t="n">
-        <v>7055206</v>
+        <v>7055257</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1741,6 +1747,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129620602</v>
+        <v>129618470</v>
       </c>
       <c r="B13" t="n">
-        <v>91588</v>
+        <v>92007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,34 +1789,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621557</v>
+        <v>621654</v>
       </c>
       <c r="R13" t="n">
-        <v>7055312</v>
+        <v>7055226</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,50 +1870,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617528</v>
+        <v>129618548</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621607</v>
+        <v>621673</v>
       </c>
       <c r="R14" t="n">
-        <v>7055257</v>
+        <v>7055206</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1940,11 +1945,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129618407</v>
       </c>
       <c r="B2" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B4" t="n">
-        <v>91588</v>
+        <v>97645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R4" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,57 +958,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B5" t="n">
-        <v>97640</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R5" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,12 +1059,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
         <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,40 +1778,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B13" t="n">
-        <v>92007</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R13" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1870,49 +1879,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>92012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R14" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1974,7 +1974,7 @@
         <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129617589</v>
       </c>
       <c r="B17" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -873,45 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>97645</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R4" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -958,61 +962,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>97645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R5" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,12 +1059,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129620602</v>
+        <v>129617528</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621557</v>
+        <v>621607</v>
       </c>
       <c r="R11" t="n">
-        <v>7055312</v>
+        <v>7055257</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,50 +1681,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617528</v>
+        <v>129618548</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621607</v>
+        <v>621673</v>
       </c>
       <c r="R12" t="n">
-        <v>7055257</v>
+        <v>7055206</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,49 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618548</v>
+        <v>129620602</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621673</v>
+        <v>621557</v>
       </c>
       <c r="R13" t="n">
-        <v>7055206</v>
+        <v>7055312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617528</v>
+        <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,39 +1585,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621607</v>
+        <v>621557</v>
       </c>
       <c r="R11" t="n">
-        <v>7055257</v>
+        <v>7055312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,11 +1645,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,49 +1671,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R12" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1782,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129620602</v>
+        <v>129617528</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,34 +1774,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621557</v>
+        <v>621607</v>
       </c>
       <c r="R13" t="n">
-        <v>7055312</v>
+        <v>7055257</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1853,6 +1839,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,40 +1870,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B14" t="n">
-        <v>92012</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R14" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129620602</v>
+        <v>129617528</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621557</v>
+        <v>621607</v>
       </c>
       <c r="R11" t="n">
-        <v>7055312</v>
+        <v>7055257</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618470</v>
+        <v>129620602</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,29 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621654</v>
+        <v>621557</v>
       </c>
       <c r="R12" t="n">
-        <v>7055226</v>
+        <v>7055312</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1763,50 +1778,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617528</v>
+        <v>129618548</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621607</v>
+        <v>621673</v>
       </c>
       <c r="R13" t="n">
-        <v>7055257</v>
+        <v>7055206</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1839,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1870,49 +1879,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>92012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R14" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>97645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R15" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B16" t="n">
-        <v>97645</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R16" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,38 +1071,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1111,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R6" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1147,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,37 +1172,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1217,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R7" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1253,6 +1248,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617528</v>
+        <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,39 +1585,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621607</v>
+        <v>621557</v>
       </c>
       <c r="R11" t="n">
-        <v>7055257</v>
+        <v>7055312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,11 +1645,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129620602</v>
+        <v>129618470</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>92016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1682,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621557</v>
+        <v>621654</v>
       </c>
       <c r="R12" t="n">
-        <v>7055312</v>
+        <v>7055226</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,49 +1763,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618548</v>
+        <v>129617528</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621673</v>
+        <v>621607</v>
       </c>
       <c r="R13" t="n">
-        <v>7055206</v>
+        <v>7055257</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1853,6 +1839,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,40 +1870,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B14" t="n">
-        <v>92012</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R14" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>97645</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R15" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>97649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R16" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2265,7 +2265,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,37 +1071,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1110,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R6" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1146,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,38 +1178,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R7" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1248,11 +1253,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129620602</v>
+        <v>129617528</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621557</v>
+        <v>621607</v>
       </c>
       <c r="R11" t="n">
-        <v>7055312</v>
+        <v>7055257</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,40 +1681,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B12" t="n">
-        <v>92016</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R12" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1763,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617528</v>
+        <v>129620602</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,39 +1793,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621607</v>
+        <v>621557</v>
       </c>
       <c r="R13" t="n">
-        <v>7055257</v>
+        <v>7055312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1839,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1870,49 +1879,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>92018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R14" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1974,7 +1974,7 @@
         <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1071,38 +1071,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1111,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R6" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1147,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,37 +1172,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1217,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R7" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1253,6 +1248,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,37 +1071,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1110,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R6" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1146,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,38 +1178,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R7" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1248,11 +1253,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,49 +1681,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618548</v>
+        <v>129620602</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621673</v>
+        <v>621557</v>
       </c>
       <c r="R12" t="n">
-        <v>7055206</v>
+        <v>7055312</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1782,45 +1778,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129620602</v>
+        <v>129618548</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621557</v>
+        <v>621673</v>
       </c>
       <c r="R13" t="n">
-        <v>7055312</v>
+        <v>7055206</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2071,7 +2071,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>97661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R15" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B16" t="n">
-        <v>97661</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R16" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>97661</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R15" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>97661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R16" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129618407</v>
       </c>
       <c r="B2" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>97665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R4" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,57 +958,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B5" t="n">
-        <v>97661</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R5" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,12 +1059,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129617528</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129620602</v>
+        <v>129618470</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>92021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621557</v>
+        <v>621654</v>
       </c>
       <c r="R12" t="n">
-        <v>7055312</v>
+        <v>7055226</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,49 +1778,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618548</v>
+        <v>129620602</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621673</v>
+        <v>621557</v>
       </c>
       <c r="R13" t="n">
-        <v>7055206</v>
+        <v>7055312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1879,40 +1875,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618470</v>
+        <v>129618548</v>
       </c>
       <c r="B14" t="n">
-        <v>92018</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621654</v>
+        <v>621673</v>
       </c>
       <c r="R14" t="n">
-        <v>7055226</v>
+        <v>7055206</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1971,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>97665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R15" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B16" t="n">
-        <v>97661</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R16" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2168,7 +2173,7 @@
         <v>129617589</v>
       </c>
       <c r="B17" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2270,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2367,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2473,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,7 +2574,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617528</v>
+        <v>129620602</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,39 +1585,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621607</v>
+        <v>621557</v>
       </c>
       <c r="R11" t="n">
-        <v>7055257</v>
+        <v>7055312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,11 +1645,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129618470</v>
+        <v>129617528</v>
       </c>
       <c r="B12" t="n">
-        <v>92021</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1682,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621654</v>
+        <v>621607</v>
       </c>
       <c r="R12" t="n">
-        <v>7055226</v>
+        <v>7055257</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,6 +1747,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,45 +1778,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129620602</v>
+        <v>129618548</v>
       </c>
       <c r="B13" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621557</v>
+        <v>621673</v>
       </c>
       <c r="R13" t="n">
-        <v>7055312</v>
+        <v>7055206</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,49 +1879,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>92021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R14" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129620372</v>
+        <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>97665</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621724</v>
+        <v>621722</v>
       </c>
       <c r="R15" t="n">
-        <v>7055308</v>
+        <v>7055317</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129620379</v>
+        <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>97665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621722</v>
+        <v>621724</v>
       </c>
       <c r="R16" t="n">
-        <v>7055317</v>
+        <v>7055308</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129618407</v>
       </c>
       <c r="B2" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129620440</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,45 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>97665</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R4" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -958,61 +962,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R5" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,50 +1059,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1111,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R6" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1147,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,37 +1172,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1217,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R7" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1253,6 +1248,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,7 +1282,7 @@
         <v>129618528</v>
       </c>
       <c r="B8" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129618473</v>
       </c>
       <c r="B9" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129619583</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129620602</v>
+        <v>129617528</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621557</v>
+        <v>621607</v>
       </c>
       <c r="R11" t="n">
-        <v>7055312</v>
+        <v>7055257</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,50 +1681,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617528</v>
+        <v>129618548</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbäcken, Finnbäcken, Ång</t>
+          <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621607</v>
+        <v>621673</v>
       </c>
       <c r="R12" t="n">
-        <v>7055257</v>
+        <v>7055206</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,49 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129618548</v>
+        <v>129618470</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>92024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621673</v>
+        <v>621654</v>
       </c>
       <c r="R13" t="n">
-        <v>7055206</v>
+        <v>7055226</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129618470</v>
+        <v>129620602</v>
       </c>
       <c r="B14" t="n">
-        <v>92021</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,34 +1890,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Långmyran, Södra Långmyran, Ång</t>
+          <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621654</v>
+        <v>621557</v>
       </c>
       <c r="R14" t="n">
-        <v>7055226</v>
+        <v>7055312</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1979,7 +1979,7 @@
         <v>129620379</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129620372</v>
       </c>
       <c r="B16" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>129617589</v>
       </c>
       <c r="B17" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129620306</v>
       </c>
       <c r="B18" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>129620489</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>129619813</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>129620513</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -873,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R4" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,57 +958,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R5" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,49 +1059,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129619846</v>
+        <v>129618167</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1110,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621739</v>
+        <v>621615</v>
       </c>
       <c r="R6" t="n">
-        <v>7055218</v>
+        <v>7055163</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1146,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,38 +1178,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618167</v>
+        <v>129619846</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621615</v>
+        <v>621739</v>
       </c>
       <c r="R7" t="n">
-        <v>7055163</v>
+        <v>7055218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1248,11 +1253,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 44996-2025 artfynd.xlsx
+++ b/artfynd/A 44996-2025 artfynd.xlsx
@@ -873,45 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129618239</v>
+        <v>129618400</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621650</v>
+        <v>621669</v>
       </c>
       <c r="R4" t="n">
-        <v>7055187</v>
+        <v>7055205</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -958,61 +962,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129618400</v>
+        <v>129618239</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Långmyran, Södra Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621669</v>
+        <v>621650</v>
       </c>
       <c r="R5" t="n">
-        <v>7055205</v>
+        <v>7055187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,12 +1059,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
